--- a/results/test_predictions.xlsx
+++ b/results/test_predictions.xlsx
@@ -16,14 +16,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +48,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,1173 +435,1171 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 0.0833333333333333</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 10; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 0.0833333333333333</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 15; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 1; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 1; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 0.0833333333333333</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 20; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 0.0833333333333333</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 25; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 2; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 2; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 0.0833333333333333</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 30; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 3; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 3; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 4; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 4; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 5; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 5; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 6; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 6; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 7; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="FY1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="FZ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="GA1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="GB1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="GC1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="GD1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="GE1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="GF1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="GG1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="GH1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="GI1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="GJ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="GK1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 7; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 8; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 0.25</t>
+        </is>
+      </c>
+      <c r="GN1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 0.5</t>
+        </is>
+      </c>
+      <c r="GO1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 0.75</t>
+        </is>
+      </c>
+      <c r="GP1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 1</t>
+        </is>
+      </c>
+      <c r="GQ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 1.5</t>
+        </is>
+      </c>
+      <c r="GR1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="GS1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="GT1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 2</t>
+        </is>
+      </c>
+      <c r="GU1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="GV1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="GW1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 3</t>
+        </is>
+      </c>
+      <c r="GX1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="GY1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 4</t>
+        </is>
+      </c>
+      <c r="GZ1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 5</t>
+        </is>
+      </c>
+      <c r="HA1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 8; Maturity : 7</t>
+        </is>
+      </c>
+      <c r="HB1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 0.0833333333333333</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 0.0833333333333333</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 0.0833333333333333</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 0.0833333333333333</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 0.0833333333333333</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 0.0833333333333333</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
+      <c r="HC1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 0.25</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 0.25</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
+      <c r="HD1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 0.5</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 0.5</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="HE1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 0.75</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 0.75</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
+      <c r="HF1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 1</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 1</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
+      <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 1.5</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="CG1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 1.5</t>
-        </is>
-      </c>
-      <c r="CH1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CI1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CJ1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CK1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CL1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
+      <c r="HH1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 9; Maturity : 10</t>
+        </is>
+      </c>
+      <c r="HI1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 9; Maturity : 15</t>
+        </is>
+      </c>
+      <c r="HJ1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 2</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 2</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
+      <c r="HK1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 9; Maturity : 20</t>
+        </is>
+      </c>
+      <c r="HL1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 9; Maturity : 25</t>
+        </is>
+      </c>
+      <c r="HM1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 3</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 3</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
+      <c r="HN1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor : 9; Maturity : 30</t>
+        </is>
+      </c>
+      <c r="HO1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 4</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 4</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
+      <c r="HP1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 5</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 5</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
+      <c r="HQ1" s="1" t="inlineStr">
         <is>
           <t>Tenor : 9; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 7</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FG1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FH1" t="inlineStr">
-        <is>
-          <t>Tenor : 9; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FI1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FJ1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FK1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FL1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FM1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 10</t>
-        </is>
-      </c>
-      <c r="FN1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FO1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FP1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FQ1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FR1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FS1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FT1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FU1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FV1" t="inlineStr">
-        <is>
-          <t>Tenor : 9; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FW1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FX1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FY1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="FZ1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="GA1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 15</t>
-        </is>
-      </c>
-      <c r="GB1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GC1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GD1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GE1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GF1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GG1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GH1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GI1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GJ1" t="inlineStr">
-        <is>
-          <t>Tenor : 9; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GK1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GL1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GM1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GN1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GO1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 20</t>
-        </is>
-      </c>
-      <c r="GP1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GQ1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GR1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GS1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GT1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GU1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GV1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GW1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GX1" t="inlineStr">
-        <is>
-          <t>Tenor : 9; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GY1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="GZ1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="HA1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="HB1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="HC1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 25</t>
-        </is>
-      </c>
-      <c r="HD1" t="inlineStr">
-        <is>
-          <t>Tenor : 1; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HE1" t="inlineStr">
-        <is>
-          <t>Tenor : 2; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HF1" t="inlineStr">
-        <is>
-          <t>Tenor : 3; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HG1" t="inlineStr">
-        <is>
-          <t>Tenor : 4; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HH1" t="inlineStr">
-        <is>
-          <t>Tenor : 5; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HI1" t="inlineStr">
-        <is>
-          <t>Tenor : 6; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HJ1" t="inlineStr">
-        <is>
-          <t>Tenor : 7; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HK1" t="inlineStr">
-        <is>
-          <t>Tenor : 8; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HL1" t="inlineStr">
-        <is>
-          <t>Tenor : 9; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HM1" t="inlineStr">
-        <is>
-          <t>Tenor : 10; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HN1" t="inlineStr">
-        <is>
-          <t>Tenor : 15; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HO1" t="inlineStr">
-        <is>
-          <t>Tenor : 20; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HP1" t="inlineStr">
-        <is>
-          <t>Tenor : 25; Maturity : 30</t>
-        </is>
-      </c>
-      <c r="HQ1" t="inlineStr">
-        <is>
-          <t>Tenor : 30; Maturity : 30</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>24/12/2051</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>55511</v>
       </c>
       <c r="B2" t="n">
         <v>0.03848225370011232</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06838420595653906</v>
+        <v>0.06838420595653905</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09492429407562031</v>
+        <v>0.09492429407562027</v>
       </c>
       <c r="E2" t="n">
         <v>0.116086942359324</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1366313755947939</v>
+        <v>0.1366313755947938</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1587412764146939</v>
+        <v>0.1587412764146938</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2612219680449814</v>
+        <v>0.2612219680449813</v>
       </c>
       <c r="I2" t="n">
         <v>0.2839301368823654</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1852299230486858</v>
+        <v>0.1852299230486856</v>
       </c>
       <c r="K2" t="n">
-        <v>0.306648770794299</v>
+        <v>0.3066487707942989</v>
       </c>
       <c r="L2" t="n">
         <v>0.3256565621189813</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2074877809817465</v>
+        <v>0.2074877809817464</v>
       </c>
       <c r="N2" t="n">
         <v>0.3436895690901638</v>
@@ -1592,7 +1608,7 @@
         <v>0.2235406688017278</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2414201192200382</v>
+        <v>0.2414201192200381</v>
       </c>
       <c r="Q2" t="n">
         <v>0.2556931922812655</v>
@@ -1601,31 +1617,31 @@
         <v>0.03732081839708534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06489532155366672</v>
+        <v>0.06489532155366669</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0893690811210906</v>
+        <v>0.08936908112109054</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1102613303145226</v>
+        <v>0.1102613303145225</v>
       </c>
       <c r="V2" t="n">
         <v>0.1264709684400258</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1533877330712442</v>
+        <v>0.1533877330712441</v>
       </c>
       <c r="X2" t="n">
         <v>0.2628372779769167</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2818253227170215</v>
+        <v>0.2818253227170214</v>
       </c>
       <c r="Z2" t="n">
         <v>0.1688809441931666</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3116353309799021</v>
+        <v>0.3116353309799022</v>
       </c>
       <c r="AB2" t="n">
         <v>0.3374091857695936</v>
@@ -1640,25 +1656,25 @@
         <v>0.2179072636605746</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2271429144172106</v>
+        <v>0.2271429144172105</v>
       </c>
       <c r="AG2" t="n">
         <v>0.2513551093535868</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.02743264668258015</v>
+        <v>0.02743264668258017</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.05334149310658427</v>
+        <v>0.05334149310658435</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.08607960303007985</v>
+        <v>0.08607960303007996</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.116534905546824</v>
+        <v>0.1165349055468241</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.148795055039431</v>
+        <v>0.1487950550394311</v>
       </c>
       <c r="AM2" t="n">
         <v>0.1898571666656045</v>
@@ -1670,7 +1686,7 @@
         <v>0.290675303076694</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.218823209501211</v>
+        <v>0.2188232095012109</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.3085614939838798</v>
@@ -1685,7 +1701,7 @@
         <v>0.3440568001447152</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2725807195541967</v>
+        <v>0.2725807195541965</v>
       </c>
       <c r="AV2" t="n">
         <v>0.2863704111074003</v>
@@ -1694,19 +1710,19 @@
         <v>0.2922890357146349</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.03564526857743808</v>
+        <v>0.03564526857743807</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.06150998293490059</v>
+        <v>0.06150998293490056</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.08669523353513596</v>
+        <v>0.08669523353513593</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1077244350201244</v>
+        <v>0.1077244350201243</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1246242438286684</v>
+        <v>0.1246242438286683</v>
       </c>
       <c r="BC2" t="n">
         <v>0.1446979880151395</v>
@@ -1718,10 +1734,10 @@
         <v>0.2913605530407852</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1646745132162523</v>
+        <v>0.1646745132162522</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.3164993542111663</v>
+        <v>0.3164993542111662</v>
       </c>
       <c r="BH2" t="n">
         <v>0.3506776832600154</v>
@@ -1730,10 +1746,10 @@
         <v>0.195732198283345</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.3789929980768074</v>
+        <v>0.3789929980768073</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.2151104955673085</v>
+        <v>0.2151104955673084</v>
       </c>
       <c r="BL2" t="n">
         <v>0.2295607253538771</v>
@@ -1742,37 +1758,37 @@
         <v>0.2500467958483066</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.03549790043220302</v>
+        <v>0.035497900432203</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.06140992723511271</v>
+        <v>0.06140992723511269</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.08905504095635608</v>
+        <v>0.08905504095635604</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.1060625486916267</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.1236643177893607</v>
+        <v>0.1236643177893606</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1445064511451257</v>
+        <v>0.1445064511451256</v>
       </c>
       <c r="BT2" t="n">
         <v>0.2723490952867149</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.2957960464126875</v>
+        <v>0.2957960464126876</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1638875974732449</v>
+        <v>0.1638875974732448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.3315837974988083</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.362764299527861</v>
+        <v>0.3627642995278609</v>
       </c>
       <c r="BY2" t="n">
         <v>0.1933926997654514</v>
@@ -1781,7 +1797,7 @@
         <v>0.3570233519628013</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2168921749002229</v>
+        <v>0.2168921749002228</v>
       </c>
       <c r="CB2" t="n">
         <v>0.2291200537730613</v>
@@ -1790,31 +1806,31 @@
         <v>0.2488676991420224</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.03622732910068605</v>
+        <v>0.03622732910068608</v>
       </c>
       <c r="CE2" t="n">
         <v>0.06570686643615213</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.1001931030408769</v>
+        <v>0.100193103040877</v>
       </c>
       <c r="CG2" t="n">
         <v>0.12839200246351</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.1538450544020197</v>
+        <v>0.1538450544020196</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1896680475362002</v>
+        <v>0.1896680475362001</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.2893560421962454</v>
+        <v>0.2893560421962453</v>
       </c>
       <c r="CK2" t="n">
         <v>0.2905099833838228</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.2194436851002717</v>
+        <v>0.2194436851002716</v>
       </c>
       <c r="CM2" t="n">
         <v>0.3093319199575731</v>
@@ -1823,37 +1839,37 @@
         <v>0.3311963289958924</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.2444186822261233</v>
+        <v>0.2444186822261231</v>
       </c>
       <c r="CP2" t="n">
         <v>0.3385052153576347</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.2662400929360156</v>
+        <v>0.2662400929360155</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.275238426478556</v>
+        <v>0.2752384264785559</v>
       </c>
       <c r="CS2" t="n">
         <v>0.2858192565704155</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.03588714866225379</v>
+        <v>0.03588714866225377</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.06244692414289284</v>
+        <v>0.06244692414289282</v>
       </c>
       <c r="CV2" t="n">
         <v>0.08945670482838607</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.1090224494671968</v>
+        <v>0.1090224494671967</v>
       </c>
       <c r="CX2" t="n">
         <v>0.1229877694123952</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.1473011382068523</v>
+        <v>0.1473011382068522</v>
       </c>
       <c r="CZ2" t="n">
         <v>0.2823550584263984</v>
@@ -1862,19 +1878,19 @@
         <v>0.3103909333209407</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.1703081323780817</v>
+        <v>0.1703081323780816</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.3402725463850311</v>
+        <v>0.3402725463850312</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.3563896859354028</v>
+        <v>0.3563896859354029</v>
       </c>
       <c r="DE2" t="n">
         <v>0.1949990347761683</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.3441632925969054</v>
+        <v>0.3441632925969053</v>
       </c>
       <c r="DG2" t="n">
         <v>0.218134935011923</v>
@@ -1886,10 +1902,10 @@
         <v>0.260302234655152</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0384433373208394</v>
+        <v>0.03844333732083941</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.06923150135957032</v>
+        <v>0.06923150135957033</v>
       </c>
       <c r="DL2" t="n">
         <v>0.1014325266787925</v>
@@ -1901,7 +1917,7 @@
         <v>0.1531881646222611</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.1851530114466139</v>
+        <v>0.1851530114466138</v>
       </c>
       <c r="DP2" t="n">
         <v>0.2781204875356655</v>
@@ -1910,34 +1926,34 @@
         <v>0.2823625416386618</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.2138970262227884</v>
+        <v>0.2138970262227883</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.3108240109761441</v>
+        <v>0.310824010976144</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.3314757499097072</v>
+        <v>0.3314757499097071</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.241226330229459</v>
+        <v>0.2412263302294589</v>
       </c>
       <c r="DV2" t="n">
         <v>0.3408223084893525</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2578178640071286</v>
+        <v>0.2578178640071285</v>
       </c>
       <c r="DX2" t="n">
         <v>0.2726386588717989</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.2801036613789783</v>
+        <v>0.2801036613789781</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.04013965663167024</v>
+        <v>0.04013965663167026</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.07031593546844987</v>
+        <v>0.07031593546844989</v>
       </c>
       <c r="EB2" t="n">
         <v>0.1034632855707534</v>
@@ -1946,13 +1962,13 @@
         <v>0.1304318841944188</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.1503962022759053</v>
+        <v>0.1503962022759052</v>
       </c>
       <c r="EE2" t="n">
         <v>0.1852946698944458</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.2798276536161978</v>
+        <v>0.2798276536161977</v>
       </c>
       <c r="EG2" t="n">
         <v>0.2801741321667732</v>
@@ -1976,13 +1992,13 @@
         <v>0.2551104309875756</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.2637045705913952</v>
+        <v>0.2637045705913951</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.2719956598862831</v>
+        <v>0.271995659886283</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04075330068332524</v>
+        <v>0.04075330068332526</v>
       </c>
       <c r="EQ2" t="n">
         <v>0.07175775072771369</v>
@@ -1997,7 +2013,7 @@
         <v>0.1490823643226737</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.1799805134353617</v>
+        <v>0.1799805134353616</v>
       </c>
       <c r="EV2" t="n">
         <v>0.2697108821725389</v>
@@ -2021,19 +2037,19 @@
         <v>0.3472964405078915</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.2463952848707599</v>
+        <v>0.2463952848707598</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.2604637135973949</v>
+        <v>0.2604637135973948</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.2748879062091236</v>
+        <v>0.2748879062091235</v>
       </c>
       <c r="FF2" t="n">
         <v>0.0399716305430009</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.06881218858230677</v>
+        <v>0.0688121885823068</v>
       </c>
       <c r="FH2" t="n">
         <v>0.1027053682378533</v>
@@ -2042,13 +2058,13 @@
         <v>0.1231334473207236</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.1417308789692867</v>
+        <v>0.1417308789692866</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.1746770307883345</v>
+        <v>0.1746770307883344</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.2708709940091098</v>
+        <v>0.2708709940091099</v>
       </c>
       <c r="FM2" t="n">
         <v>0.2834230112410702</v>
@@ -2057,7 +2073,7 @@
         <v>0.1944680083243056</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.3066920202976034</v>
+        <v>0.3066920202976033</v>
       </c>
       <c r="FP2" t="n">
         <v>0.3246113784992311</v>
@@ -2069,31 +2085,31 @@
         <v>0.3458564126342756</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.2463693733267779</v>
+        <v>0.2463693733267778</v>
       </c>
       <c r="FT2" t="n">
         <v>0.2537025986350097</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.2627751686484756</v>
+        <v>0.2627751686484754</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.03941886017117559</v>
+        <v>0.0394188601711756</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.06999142833210631</v>
+        <v>0.0699914283321063</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.09926531748489274</v>
+        <v>0.09926531748489272</v>
       </c>
       <c r="FY2" t="n">
         <v>0.1233536227819295</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.1407114317998537</v>
+        <v>0.1407114317998536</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.1705409270747136</v>
+        <v>0.1705409270747135</v>
       </c>
       <c r="GB2" t="n">
         <v>0.2704778666616052</v>
@@ -2105,22 +2121,22 @@
         <v>0.1941838092092232</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.3029524961117126</v>
+        <v>0.3029524961117125</v>
       </c>
       <c r="GF2" t="n">
         <v>0.3299098025672603</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.2223305230520491</v>
+        <v>0.222330523052049</v>
       </c>
       <c r="GH2" t="n">
         <v>0.3491532951272823</v>
       </c>
       <c r="GI2" t="n">
-        <v>0.2380610954715996</v>
+        <v>0.2380610954715995</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.2494210704690925</v>
+        <v>0.2494210704690924</v>
       </c>
       <c r="GK2" t="n">
         <v>0.2624898510506561</v>
@@ -2129,37 +2145,37 @@
         <v>0.03911068882897794</v>
       </c>
       <c r="GM2" t="n">
-        <v>0.06913993387830231</v>
+        <v>0.06913993387830229</v>
       </c>
       <c r="GN2" t="n">
-        <v>0.09767081352376068</v>
+        <v>0.09767081352376067</v>
       </c>
       <c r="GO2" t="n">
-        <v>0.1217746687738796</v>
+        <v>0.1217746687738795</v>
       </c>
       <c r="GP2" t="n">
         <v>0.137216716642038</v>
       </c>
       <c r="GQ2" t="n">
-        <v>0.1665106713146519</v>
+        <v>0.1665106713146518</v>
       </c>
       <c r="GR2" t="n">
-        <v>0.2670035762651374</v>
+        <v>0.2670035762651373</v>
       </c>
       <c r="GS2" t="n">
         <v>0.2819466902382571</v>
       </c>
       <c r="GT2" t="n">
-        <v>0.1868514066601901</v>
+        <v>0.18685140666019</v>
       </c>
       <c r="GU2" t="n">
-        <v>0.3020762077136136</v>
+        <v>0.3020762077136135</v>
       </c>
       <c r="GV2" t="n">
         <v>0.3243599286051349</v>
       </c>
       <c r="GW2" t="n">
-        <v>0.2165626245519423</v>
+        <v>0.2165626245519422</v>
       </c>
       <c r="GX2" t="n">
         <v>0.3430950653942935</v>
@@ -2186,10 +2202,10 @@
         <v>0.1208348883575699</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.1357531321517226</v>
+        <v>0.1357531321517225</v>
       </c>
       <c r="HG2" t="n">
-        <v>0.1637094215310925</v>
+        <v>0.1637094215310924</v>
       </c>
       <c r="HH2" t="n">
         <v>0.2625072851245144</v>
@@ -2198,7 +2214,7 @@
         <v>0.2835263584745253</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.18502985399036</v>
+        <v>0.1850298539903599</v>
       </c>
       <c r="HK2" t="n">
         <v>0.303187280108406</v>
@@ -2207,35 +2223,33 @@
         <v>0.3254381428582635</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.2138686129786425</v>
+        <v>0.2138686129786424</v>
       </c>
       <c r="HN2" t="n">
         <v>0.3457474644484548</v>
       </c>
       <c r="HO2" t="n">
-        <v>0.2279049036383497</v>
+        <v>0.2279049036383496</v>
       </c>
       <c r="HP2" t="n">
-        <v>0.2441888712644371</v>
+        <v>0.244188871264437</v>
       </c>
       <c r="HQ2" t="n">
-        <v>0.2573894732967042</v>
+        <v>0.2573894732967041</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>26/12/2051</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>55513</v>
       </c>
       <c r="B3" t="n">
         <v>0.03821641790654814</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06816866263519518</v>
+        <v>0.06816866263519515</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09481710556347345</v>
+        <v>0.09481710556347341</v>
       </c>
       <c r="E3" t="n">
         <v>0.1160187575223641</v>
@@ -2244,13 +2258,13 @@
         <v>0.1368263956435865</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1589404616387766</v>
+        <v>0.1589404616387765</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2603028786836096</v>
+        <v>0.2603028786836097</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2827685921214747</v>
+        <v>0.2827685921214746</v>
       </c>
       <c r="J3" t="n">
         <v>0.18567855631191</v>
@@ -2265,25 +2279,25 @@
         <v>0.2075819555442231</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3411159507879309</v>
+        <v>0.3411159507879311</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2232731585294692</v>
+        <v>0.2232731585294691</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2412559792077152</v>
+        <v>0.2412559792077151</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2550217442832061</v>
+        <v>0.255021744283206</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03715563596282515</v>
+        <v>0.03715563596282514</v>
       </c>
       <c r="S3" t="n">
         <v>0.06480434796306307</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08925924200545381</v>
+        <v>0.08925924200545376</v>
       </c>
       <c r="U3" t="n">
         <v>0.1103001562920604</v>
@@ -2301,10 +2315,10 @@
         <v>0.2806073249738028</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1689816335767888</v>
+        <v>0.1689816335767887</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.3101694565199241</v>
+        <v>0.3101694565199242</v>
       </c>
       <c r="AB3" t="n">
         <v>0.3352662635076484</v>
@@ -2316,7 +2330,7 @@
         <v>0.3629041358294767</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2177219624150177</v>
+        <v>0.2177219624150176</v>
       </c>
       <c r="AF3" t="n">
         <v>0.2266816149406709</v>
@@ -2325,25 +2339,25 @@
         <v>0.2506513221904655</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0264548244913741</v>
+        <v>0.02645482449137414</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.05185409314191112</v>
+        <v>0.05185409314191117</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.08446757992711766</v>
+        <v>0.0844675799271178</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1148382655836722</v>
+        <v>0.1148382655836723</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1474990550214182</v>
+        <v>0.1474990550214183</v>
       </c>
       <c r="AM3" t="n">
         <v>0.1887093765938681</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.2888834511409504</v>
+        <v>0.2888834511409503</v>
       </c>
       <c r="AO3" t="n">
         <v>0.2894292850106603</v>
@@ -2352,25 +2366,25 @@
         <v>0.2185165039145371</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.3074109668043061</v>
+        <v>0.3074109668043062</v>
       </c>
       <c r="AR3" t="n">
         <v>0.3341169794393203</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.2570888799394663</v>
+        <v>0.2570888799394662</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.3411428989753162</v>
+        <v>0.3411428989753163</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2727415742562457</v>
+        <v>0.2727415742562456</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2865291996830826</v>
+        <v>0.2865291996830824</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2924728360196007</v>
+        <v>0.2924728360196006</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0354583533461697</v>
@@ -2379,7 +2393,7 @@
         <v>0.0613347472956085</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.08660847088155162</v>
+        <v>0.08660847088155156</v>
       </c>
       <c r="BA3" t="n">
         <v>0.107734719436789</v>
@@ -2397,10 +2411,10 @@
         <v>0.2900291448483948</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1646092068702732</v>
+        <v>0.1646092068702731</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.3147596789815145</v>
+        <v>0.3147596789815144</v>
       </c>
       <c r="BH3" t="n">
         <v>0.3487244622698299</v>
@@ -2409,7 +2423,7 @@
         <v>0.1957385582737311</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.3761795752352762</v>
+        <v>0.3761795752352763</v>
       </c>
       <c r="BK3" t="n">
         <v>0.2149883881178857</v>
@@ -2424,10 +2438,10 @@
         <v>0.03532251607796678</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.06127264590588564</v>
+        <v>0.06127264590588562</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.08899572223026279</v>
+        <v>0.08899572223026277</v>
       </c>
       <c r="BQ3" t="n">
         <v>0.1060025324925042</v>
@@ -2445,22 +2459,22 @@
         <v>0.2943378563917817</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1636922704323188</v>
+        <v>0.1636922704323189</v>
       </c>
       <c r="BW3" t="n">
         <v>0.3297177899394331</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.3604938094804593</v>
+        <v>0.3604938094804594</v>
       </c>
       <c r="BY3" t="n">
         <v>0.1932388942763625</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.354533043331951</v>
+        <v>0.3545330433319511</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.216544213357129</v>
+        <v>0.2165442133571289</v>
       </c>
       <c r="CB3" t="n">
         <v>0.2284446223980988</v>
@@ -2469,13 +2483,13 @@
         <v>0.2480085423626025</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.03538231803285648</v>
+        <v>0.03538231803285653</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0644847700940268</v>
+        <v>0.06448477009402685</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.09887496349683457</v>
+        <v>0.09887496349683465</v>
       </c>
       <c r="CG3" t="n">
         <v>0.1273124662239279</v>
@@ -2484,46 +2498,46 @@
         <v>0.1530282387837954</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1893610116904555</v>
+        <v>0.1893610116904554</v>
       </c>
       <c r="CJ3" t="n">
         <v>0.2886294157089217</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.2892930952747446</v>
+        <v>0.2892930952747447</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.2196826873204735</v>
+        <v>0.2196826873204733</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.3082040506342388</v>
+        <v>0.3082040506342389</v>
       </c>
       <c r="CN3" t="n">
         <v>0.3296337430612739</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.2448450301731816</v>
+        <v>0.2448450301731815</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.3354932461016527</v>
+        <v>0.3354932461016528</v>
       </c>
       <c r="CQ3" t="n">
         <v>0.2662671073215886</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.2755236061164966</v>
+        <v>0.2755236061164965</v>
       </c>
       <c r="CS3" t="n">
         <v>0.2856521873397019</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.03570566696385737</v>
+        <v>0.03570566696385736</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.06227222771848772</v>
+        <v>0.06227222771848771</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.08941019142380797</v>
+        <v>0.08941019142380795</v>
       </c>
       <c r="CW3" t="n">
         <v>0.1090077020058036</v>
@@ -2541,19 +2555,19 @@
         <v>0.308823220250163</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.1701322831716066</v>
+        <v>0.1701322831716065</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.3383814341802915</v>
+        <v>0.3383814341802916</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.3545059473937075</v>
+        <v>0.3545059473937076</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1946548976390976</v>
+        <v>0.1946548976390975</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.3420630672201292</v>
+        <v>0.3420630672201293</v>
       </c>
       <c r="DG3" t="n">
         <v>0.2176737189265787</v>
@@ -2565,22 +2579,22 @@
         <v>0.2591563330890087</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.03766849246141239</v>
+        <v>0.03766849246141242</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.06813871268129323</v>
+        <v>0.06813871268129329</v>
       </c>
       <c r="DL3" t="n">
         <v>0.1003594475409765</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.1287528265045705</v>
+        <v>0.1287528265045704</v>
       </c>
       <c r="DN3" t="n">
         <v>0.1526920390112623</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.1849397054873806</v>
+        <v>0.1849397054873805</v>
       </c>
       <c r="DP3" t="n">
         <v>0.2773744316409549</v>
@@ -2589,7 +2603,7 @@
         <v>0.281203538933839</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2140070193883249</v>
+        <v>0.2140070193883248</v>
       </c>
       <c r="DS3" t="n">
         <v>0.3096618109208447</v>
@@ -2604,7 +2618,7 @@
         <v>0.3379436682496434</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2582034101409074</v>
+        <v>0.2582034101409073</v>
       </c>
       <c r="DX3" t="n">
         <v>0.2728146516168122</v>
@@ -2613,10 +2627,10 @@
         <v>0.2798069429847258</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0394524631527344</v>
+        <v>0.03945246315273442</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.06946277979238059</v>
+        <v>0.06946277979238064</v>
       </c>
       <c r="EB3" t="n">
         <v>0.1027415161146497</v>
@@ -2628,7 +2642,7 @@
         <v>0.1503471371733578</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.1856079115489873</v>
+        <v>0.1856079115489872</v>
       </c>
       <c r="EF3" t="n">
         <v>0.2789767272582741</v>
@@ -2637,7 +2651,7 @@
         <v>0.279003709609825</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.2084378888140338</v>
+        <v>0.2084378888140336</v>
       </c>
       <c r="EI3" t="n">
         <v>0.3096893260242946</v>
@@ -2646,37 +2660,37 @@
         <v>0.3279478455290081</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.2377989402103841</v>
+        <v>0.2377989402103839</v>
       </c>
       <c r="EL3" t="n">
         <v>0.3451843998882409</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.2554935538136215</v>
+        <v>0.2554935538136214</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.2640576926219904</v>
+        <v>0.2640576926219901</v>
       </c>
       <c r="EO3" t="n">
         <v>0.2716698048166264</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.04019413359314684</v>
+        <v>0.04019413359314686</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0710160121422677</v>
+        <v>0.07101601214226771</v>
       </c>
       <c r="ER3" t="n">
         <v>0.1030350853946588</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1275712479261524</v>
+        <v>0.1275712479261523</v>
       </c>
       <c r="ET3" t="n">
         <v>0.1488218522138309</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.1800221171451318</v>
+        <v>0.1800221171451317</v>
       </c>
       <c r="EV3" t="n">
         <v>0.2688259875364046</v>
@@ -2685,34 +2699,34 @@
         <v>0.2849281226876989</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.2034896184067737</v>
+        <v>0.2034896184067736</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.3074756221692533</v>
+        <v>0.3074756221692534</v>
       </c>
       <c r="EZ3" t="n">
         <v>0.3292073143876553</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.2278411291188928</v>
+        <v>0.2278411291188926</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.3444661678917451</v>
+        <v>0.3444661678917452</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.2467231117601388</v>
+        <v>0.2467231117601389</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.2605094504016292</v>
+        <v>0.2605094504016291</v>
       </c>
       <c r="FE3" t="n">
         <v>0.2745939947670032</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.03948992845058349</v>
+        <v>0.0394899284505835</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.06817793587818365</v>
+        <v>0.06817793587818367</v>
       </c>
       <c r="FH3" t="n">
         <v>0.1022020722769107</v>
@@ -2721,10 +2735,10 @@
         <v>0.1228316561443759</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.1415840904789321</v>
+        <v>0.1415840904789322</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1746420755345222</v>
+        <v>0.1746420755345221</v>
       </c>
       <c r="FL3" t="n">
         <v>0.2699536047373501</v>
@@ -2733,7 +2747,7 @@
         <v>0.2822620489797124</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.1946272173120532</v>
+        <v>0.194627217312053</v>
       </c>
       <c r="FO3" t="n">
         <v>0.3055672440412209</v>
@@ -2748,7 +2762,7 @@
         <v>0.3430117842073648</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.2468492003125035</v>
+        <v>0.2468492003125034</v>
       </c>
       <c r="FT3" t="n">
         <v>0.2537548518529193</v>
@@ -2757,22 +2771,22 @@
         <v>0.2623965536608245</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.03902985637034905</v>
+        <v>0.03902985637034906</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.06950839942208585</v>
+        <v>0.06950839942208586</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.09892628520450797</v>
+        <v>0.09892628520450801</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.1231190415481033</v>
+        <v>0.1231190415481032</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.1407166705438686</v>
+        <v>0.1407166705438685</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1707520598781943</v>
+        <v>0.1707520598781942</v>
       </c>
       <c r="GB3" t="n">
         <v>0.2695326074594881</v>
@@ -2781,46 +2795,46 @@
         <v>0.2827986154567912</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1944059807799613</v>
+        <v>0.1944059807799614</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.3019393682804015</v>
+        <v>0.3019393682804014</v>
       </c>
       <c r="GF3" t="n">
         <v>0.3283288272965939</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.2226943341929454</v>
+        <v>0.2226943341929453</v>
       </c>
       <c r="GH3" t="n">
-        <v>0.346360735960245</v>
+        <v>0.3463607359602451</v>
       </c>
       <c r="GI3" t="n">
-        <v>0.2382424519300322</v>
+        <v>0.238242451930032</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.2492903991055603</v>
+        <v>0.2492903991055602</v>
       </c>
       <c r="GK3" t="n">
         <v>0.2619048188618787</v>
       </c>
       <c r="GL3" t="n">
-        <v>0.03876756690158415</v>
+        <v>0.03876756690158416</v>
       </c>
       <c r="GM3" t="n">
         <v>0.06872554087416616</v>
       </c>
       <c r="GN3" t="n">
-        <v>0.09738751129406355</v>
+        <v>0.09738751129406353</v>
       </c>
       <c r="GO3" t="n">
         <v>0.1215918883650871</v>
       </c>
       <c r="GP3" t="n">
-        <v>0.1371706110767555</v>
+        <v>0.1371706110767554</v>
       </c>
       <c r="GQ3" t="n">
-        <v>0.1666884995004997</v>
+        <v>0.1666884995004996</v>
       </c>
       <c r="GR3" t="n">
         <v>0.2660515450277332</v>
@@ -2829,22 +2843,22 @@
         <v>0.2808074303358581</v>
       </c>
       <c r="GT3" t="n">
-        <v>0.187115100196942</v>
+        <v>0.1871151001969419</v>
       </c>
       <c r="GU3" t="n">
-        <v>0.3010083923305242</v>
+        <v>0.3010083923305243</v>
       </c>
       <c r="GV3" t="n">
         <v>0.3226412117664019</v>
       </c>
       <c r="GW3" t="n">
-        <v>0.2170012201133226</v>
+        <v>0.2170012201133225</v>
       </c>
       <c r="GX3" t="n">
         <v>0.3403017112038717</v>
       </c>
       <c r="GY3" t="n">
-        <v>0.2311320286070319</v>
+        <v>0.2311320286070318</v>
       </c>
       <c r="GZ3" t="n">
         <v>0.2461554395289509</v>
@@ -2856,7 +2870,7 @@
         <v>0.03898013523934576</v>
       </c>
       <c r="HC3" t="n">
-        <v>0.06865329877159942</v>
+        <v>0.06865329877159938</v>
       </c>
       <c r="HD3" t="n">
         <v>0.09835831153767305</v>
@@ -2865,19 +2879,19 @@
         <v>0.1208058419095838</v>
       </c>
       <c r="HF3" t="n">
-        <v>0.1358683767133633</v>
+        <v>0.1358683767133632</v>
       </c>
       <c r="HG3" t="n">
         <v>0.1638961757975358</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.2615817371971706</v>
+        <v>0.2615817371971705</v>
       </c>
       <c r="HI3" t="n">
         <v>0.2823723044627902</v>
       </c>
       <c r="HJ3" t="n">
-        <v>0.1853858867664079</v>
+        <v>0.1853858867664078</v>
       </c>
       <c r="HK3" t="n">
         <v>0.3019872521317253</v>
@@ -2886,35 +2900,33 @@
         <v>0.3236419877699018</v>
       </c>
       <c r="HM3" t="n">
-        <v>0.2139364527608435</v>
+        <v>0.2139364527608434</v>
       </c>
       <c r="HN3" t="n">
-        <v>0.3430563309209047</v>
+        <v>0.3430563309209049</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.2278073875262718</v>
+        <v>0.2278073875262717</v>
       </c>
       <c r="HP3" t="n">
         <v>0.2440791200739528</v>
       </c>
       <c r="HQ3" t="n">
-        <v>0.2567180532849807</v>
+        <v>0.2567180532849806</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>27/12/2051</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>55514</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0388069787781193</v>
+        <v>0.03880697877811929</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06907301615440498</v>
+        <v>0.06907301615440496</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0959331927428167</v>
+        <v>0.09593319274281666</v>
       </c>
       <c r="E4" t="n">
         <v>0.1172646787738571</v>
@@ -2935,7 +2947,7 @@
         <v>0.1872969796012414</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3080140725407227</v>
+        <v>0.3080140725407226</v>
       </c>
       <c r="L4" t="n">
         <v>0.3267530190085972</v>
@@ -2947,28 +2959,28 @@
         <v>0.3449003709183163</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2251428982503285</v>
+        <v>0.2251428982503284</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2430513585285629</v>
+        <v>0.2430513585285628</v>
       </c>
       <c r="Q4" t="n">
         <v>0.2567160632948098</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03770565346495116</v>
+        <v>0.03770565346495117</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06563124275185926</v>
+        <v>0.06563124275185923</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09027197416234765</v>
+        <v>0.09027197416234763</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1114281363522343</v>
+        <v>0.1114281363522342</v>
       </c>
       <c r="V4" t="n">
-        <v>0.127829016172557</v>
+        <v>0.1278290161725569</v>
       </c>
       <c r="W4" t="n">
         <v>0.1550331762820331</v>
@@ -2980,13 +2992,13 @@
         <v>0.2825580790444193</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1705558100507742</v>
+        <v>0.1705558100507741</v>
       </c>
       <c r="AA4" t="n">
         <v>0.3127601760785623</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3381732327598893</v>
+        <v>0.3381732327598894</v>
       </c>
       <c r="AC4" t="n">
         <v>0.2011497711109123</v>
@@ -3004,22 +3016,22 @@
         <v>0.2523605828579867</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0270587535779216</v>
+        <v>0.02705875357792163</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.05293011893287646</v>
+        <v>0.05293011893287652</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.08599692606246995</v>
+        <v>0.08599692606246999</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1166680159215601</v>
+        <v>0.1166680159215602</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1493737120598094</v>
+        <v>0.1493737120598095</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1912452116401915</v>
+        <v>0.1912452116401916</v>
       </c>
       <c r="AN4" t="n">
         <v>0.2906574011753881</v>
@@ -3031,40 +3043,40 @@
         <v>0.2210864406851404</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.3098505736079107</v>
+        <v>0.3098505736079108</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.3367621727112094</v>
+        <v>0.3367621727112095</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.2596420317121038</v>
+        <v>0.2596420317121035</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.3446948274609987</v>
+        <v>0.3446948274609988</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2758398587195772</v>
+        <v>0.275839858719577</v>
       </c>
       <c r="AV4" t="n">
         <v>0.2893991797153599</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.2949925016781785</v>
+        <v>0.2949925016781784</v>
       </c>
       <c r="AX4" t="n">
         <v>0.03598033777744002</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.06216140099182468</v>
+        <v>0.06216140099182463</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.08763160988862366</v>
+        <v>0.08763160988862363</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1089138405364544</v>
+        <v>0.1089138405364543</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1259479530380917</v>
+        <v>0.1259479530380916</v>
       </c>
       <c r="BC4" t="n">
         <v>0.1461215608638955</v>
@@ -3073,10 +3085,10 @@
         <v>0.263987172983094</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.2919693809109382</v>
+        <v>0.2919693809109383</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1661860338443801</v>
+        <v>0.16618603384438</v>
       </c>
       <c r="BG4" t="n">
         <v>0.3172804468110715</v>
@@ -3088,13 +3100,13 @@
         <v>0.19739573481574</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.3800211342405332</v>
+        <v>0.3800211342405334</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.2165397239766902</v>
+        <v>0.2165397239766901</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.2306203717655538</v>
+        <v>0.2306203717655537</v>
       </c>
       <c r="BM4" t="n">
         <v>0.2508574713250828</v>
@@ -3103,40 +3115,40 @@
         <v>0.03584712560490493</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.06211427341748538</v>
+        <v>0.0621142734174854</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.09007230082050212</v>
+        <v>0.0900723008205021</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1072127227251114</v>
+        <v>0.1072127227251113</v>
       </c>
       <c r="BR4" t="n">
         <v>0.1249541823288101</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1458826303190452</v>
+        <v>0.1458826303190451</v>
       </c>
       <c r="BT4" t="n">
         <v>0.2727438067769736</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.2963780571865692</v>
+        <v>0.2963780571865691</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1652539868237002</v>
+        <v>0.1652539868237003</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.3323340333232652</v>
+        <v>0.3323340333232651</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.3635096620257894</v>
+        <v>0.3635096620257895</v>
       </c>
       <c r="BY4" t="n">
         <v>0.1948657195993306</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.3575205868174547</v>
+        <v>0.3575205868174549</v>
       </c>
       <c r="CA4" t="n">
         <v>0.2182226560715413</v>
@@ -3145,13 +3157,13 @@
         <v>0.2300130840319943</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.249560674633626</v>
+        <v>0.2495606746336261</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.03614487746516295</v>
+        <v>0.03614487746516298</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.06570255863616697</v>
+        <v>0.06570255863616707</v>
       </c>
       <c r="CF4" t="n">
         <v>0.1004465281039322</v>
@@ -3160,7 +3172,7 @@
         <v>0.1290777392150293</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.154911421936053</v>
+        <v>0.1549114219360531</v>
       </c>
       <c r="CI4" t="n">
         <v>0.1917467599916589</v>
@@ -3178,22 +3190,22 @@
         <v>0.3107113575837665</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.3321705622523551</v>
+        <v>0.3321705622523553</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.2475070154791941</v>
+        <v>0.2475070154791938</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.3389231571377866</v>
+        <v>0.3389231571377867</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.2691956924206529</v>
+        <v>0.2691956924206528</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.2782032591946133</v>
+        <v>0.2782032591946131</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.2880777665858078</v>
+        <v>0.2880777665858077</v>
       </c>
       <c r="CT4" t="n">
         <v>0.03623814384948224</v>
@@ -3202,19 +3214,19 @@
         <v>0.06311939485152662</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.09046987914912129</v>
+        <v>0.09046987914912126</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.1102213414491299</v>
+        <v>0.1102213414491298</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.1242123468081229</v>
+        <v>0.1242123468081228</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.1487113167682976</v>
+        <v>0.1487113167682975</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.2827472189350402</v>
+        <v>0.2827472189350403</v>
       </c>
       <c r="DA4" t="n">
         <v>0.3108954652213405</v>
@@ -3226,13 +3238,13 @@
         <v>0.3411442779791222</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.3569439847656687</v>
+        <v>0.3569439847656686</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1963581438605499</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.3443298627176454</v>
+        <v>0.3443298627176456</v>
       </c>
       <c r="DG4" t="n">
         <v>0.2193577263266979</v>
@@ -3244,10 +3256,10 @@
         <v>0.2608705202649202</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.03842981665405234</v>
+        <v>0.03842981665405235</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.06936207361616648</v>
+        <v>0.06936207361616652</v>
       </c>
       <c r="DL4" t="n">
         <v>0.1018978087108219</v>
@@ -3256,46 +3268,46 @@
         <v>0.1303737031342508</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.1543989003634058</v>
+        <v>0.1543989003634059</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.1872333330710312</v>
+        <v>0.1872333330710311</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.2790729159057035</v>
+        <v>0.2790729159057037</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.2829957612946068</v>
+        <v>0.2829957612946067</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.2164518388178352</v>
+        <v>0.2164518388178351</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.3122481991345167</v>
+        <v>0.3122481991345168</v>
       </c>
       <c r="DT4" t="n">
         <v>0.3327470055952564</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.2440687320660836</v>
+        <v>0.2440687320660835</v>
       </c>
       <c r="DV4" t="n">
         <v>0.3413425744534846</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2607424019037827</v>
+        <v>0.2607424019037828</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2755115057589419</v>
+        <v>0.2755115057589417</v>
       </c>
       <c r="DY4" t="n">
         <v>0.2821222813708252</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.04018734707529676</v>
+        <v>0.04018734707529679</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.07056801644106253</v>
+        <v>0.07056801644106254</v>
       </c>
       <c r="EB4" t="n">
         <v>0.1040993017965172</v>
@@ -3307,7 +3319,7 @@
         <v>0.1518729636938021</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.1875626668277713</v>
+        <v>0.1875626668277711</v>
       </c>
       <c r="EF4" t="n">
         <v>0.2807000186646315</v>
@@ -3316,7 +3328,7 @@
         <v>0.2808295490464428</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.2105957963069859</v>
+        <v>0.2105957963069858</v>
       </c>
       <c r="EI4" t="n">
         <v>0.3123100368593004</v>
@@ -3325,7 +3337,7 @@
         <v>0.3305047397300757</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.2403512025057001</v>
+        <v>0.2403512025056999</v>
       </c>
       <c r="EL4" t="n">
         <v>0.3486731699742343</v>
@@ -3334,13 +3346,13 @@
         <v>0.2579926434639081</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.2663456776603182</v>
+        <v>0.2663456776603181</v>
       </c>
       <c r="EO4" t="n">
         <v>0.2738081076036267</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.04088493247566975</v>
+        <v>0.04088493247566976</v>
       </c>
       <c r="EQ4" t="n">
         <v>0.07211296667872792</v>
@@ -3373,13 +3385,13 @@
         <v>0.3318366259128638</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.2301468557270554</v>
+        <v>0.2301468557270553</v>
       </c>
       <c r="FB4" t="n">
         <v>0.3480564561746173</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.2491286662635475</v>
+        <v>0.2491286662635473</v>
       </c>
       <c r="FD4" t="n">
         <v>0.262739284229394</v>
@@ -3388,7 +3400,7 @@
         <v>0.2766354044571731</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.04014206329622182</v>
+        <v>0.04014206329622184</v>
       </c>
       <c r="FG4" t="n">
         <v>0.06919234131403217</v>
@@ -3397,79 +3409,79 @@
         <v>0.1034816174719773</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.1241885697949225</v>
+        <v>0.1241885697949226</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.1431083139412715</v>
+        <v>0.1431083139412714</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.1765586031891219</v>
+        <v>0.1765586031891218</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.2716360263147563</v>
+        <v>0.2716360263147562</v>
       </c>
       <c r="FM4" t="n">
         <v>0.2841488830262952</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.1966983374570515</v>
+        <v>0.1966983374570514</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.3081212290236133</v>
+        <v>0.3081212290236132</v>
       </c>
       <c r="FP4" t="n">
         <v>0.3257429522968688</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.2256039992258466</v>
+        <v>0.2256039992258467</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.346661240252698</v>
+        <v>0.3466612402526981</v>
       </c>
       <c r="FS4" t="n">
         <v>0.2489732608757442</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.2559008014399204</v>
+        <v>0.2559008014399203</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.2643012626993837</v>
+        <v>0.2643012626993836</v>
       </c>
       <c r="FV4" t="n">
         <v>0.0396458202371746</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.07047963986192468</v>
+        <v>0.07047963986192469</v>
       </c>
       <c r="FX4" t="n">
         <v>0.1001186094771939</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.124488740934854</v>
+        <v>0.1244887409348539</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.1421195559229872</v>
+        <v>0.1421195559229871</v>
       </c>
       <c r="GA4" t="n">
         <v>0.1724505421517527</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.2712022866675419</v>
+        <v>0.2712022866675418</v>
       </c>
       <c r="GC4" t="n">
         <v>0.2847034180290112</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.1963710563778984</v>
+        <v>0.1963710563778983</v>
       </c>
       <c r="GE4" t="n">
         <v>0.3044729595963742</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.3310760015318748</v>
+        <v>0.3310760015318747</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.2247861742807848</v>
+        <v>0.2247861742807846</v>
       </c>
       <c r="GH4" t="n">
         <v>0.350083585262396</v>
@@ -3484,10 +3496,10 @@
         <v>0.2638949921450255</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.03938235341983555</v>
+        <v>0.03938235341983554</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.06967098996082169</v>
+        <v>0.06967098996082166</v>
       </c>
       <c r="GN4" t="n">
         <v>0.09854474683133475</v>
@@ -3496,19 +3508,19 @@
         <v>0.1229243576847111</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.1386053753864916</v>
+        <v>0.1386053753864915</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.1683899338065855</v>
+        <v>0.1683899338065854</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.2677186904910334</v>
+        <v>0.2677186904910333</v>
       </c>
       <c r="GS4" t="n">
         <v>0.2827309899968389</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.1889734763031572</v>
+        <v>0.1889734763031571</v>
       </c>
       <c r="GU4" t="n">
         <v>0.3035500150696638</v>
@@ -3517,7 +3529,7 @@
         <v>0.3254042689537766</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.2188750489738928</v>
+        <v>0.2188750489738927</v>
       </c>
       <c r="GX4" t="n">
         <v>0.3440403937784795</v>
@@ -3529,7 +3541,7 @@
         <v>0.2481625307129209</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.2554211226245761</v>
+        <v>0.255421122624576</v>
       </c>
       <c r="HB4" t="n">
         <v>0.0395878075886892</v>
@@ -3544,25 +3556,25 @@
         <v>0.1221082998880818</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.1372490069261487</v>
+        <v>0.1372490069261486</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.1655143385099709</v>
+        <v>0.1655143385099708</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.2632125062915916</v>
+        <v>0.2632125062915917</v>
       </c>
       <c r="HI4" t="n">
         <v>0.2843467603598235</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.1871276567101958</v>
+        <v>0.1871276567101957</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.304569780198788</v>
+        <v>0.3045697801987881</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.3264901385427355</v>
+        <v>0.3264901385427354</v>
       </c>
       <c r="HM4" t="n">
         <v>0.2158636917303149</v>
@@ -3581,13 +3593,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>29/12/2051</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>55516</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0389189680395965</v>
+        <v>0.03891896803959649</v>
       </c>
       <c r="C5" t="n">
         <v>0.06913031125792353</v>
@@ -3608,13 +3618,13 @@
         <v>0.2615587455544323</v>
       </c>
       <c r="I5" t="n">
-        <v>0.284177897412849</v>
+        <v>0.2841778974128489</v>
       </c>
       <c r="J5" t="n">
         <v>0.1866320547205501</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3070187277376725</v>
+        <v>0.3070187277376726</v>
       </c>
       <c r="L5" t="n">
         <v>0.3257204589390615</v>
@@ -3632,25 +3642,25 @@
         <v>0.2424294104230427</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2562102218367462</v>
+        <v>0.2562102218367461</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03771839972659947</v>
+        <v>0.03771839972659946</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0655467434073046</v>
+        <v>0.06554674340730458</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09015481185325654</v>
+        <v>0.09015481185325652</v>
       </c>
       <c r="U5" t="n">
         <v>0.1111782858442963</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1274513973401549</v>
+        <v>0.1274513973401548</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1545215013665678</v>
+        <v>0.1545215013665677</v>
       </c>
       <c r="X5" t="n">
         <v>0.2630703794780777</v>
@@ -3662,13 +3672,13 @@
         <v>0.1700157755099561</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3117458163701738</v>
+        <v>0.311745816370174</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.337289519301503</v>
+        <v>0.3372895193015031</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2005141286207915</v>
+        <v>0.2005141286207916</v>
       </c>
       <c r="AD5" t="n">
         <v>0.3656265989345591</v>
@@ -3683,13 +3693,13 @@
         <v>0.2518206776253084</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.02773562373085171</v>
+        <v>0.02773562373085174</v>
       </c>
       <c r="AI5" t="n">
         <v>0.05412534312015418</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.08775909647000914</v>
+        <v>0.08775909647000911</v>
       </c>
       <c r="AK5" t="n">
         <v>0.1188146368445597</v>
@@ -3716,13 +3726,13 @@
         <v>0.3358381011832766</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.2593173917306216</v>
+        <v>0.2593173917306215</v>
       </c>
       <c r="AT5" t="n">
         <v>0.3436525500708134</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2751950210893187</v>
+        <v>0.2751950210893184</v>
       </c>
       <c r="AV5" t="n">
         <v>0.288573066236752</v>
@@ -3734,7 +3744,7 @@
         <v>0.03596063525147238</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.06204058135379437</v>
+        <v>0.06204058135379435</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.08739125105338734</v>
@@ -3752,7 +3762,7 @@
         <v>0.2635132852370403</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.291238358236833</v>
+        <v>0.2912383582368329</v>
       </c>
       <c r="BF5" t="n">
         <v>0.1655948772192516</v>
@@ -3761,10 +3771,10 @@
         <v>0.3162981537980239</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.3504779728323539</v>
+        <v>0.350477972832354</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.19667523807948</v>
+        <v>0.1966752380794799</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.3787684256814214</v>
@@ -3776,7 +3786,7 @@
         <v>0.2300553561241077</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.2503708091751153</v>
+        <v>0.2503708091751152</v>
       </c>
       <c r="BN5" t="n">
         <v>0.03580288839600312</v>
@@ -3800,7 +3810,7 @@
         <v>0.2722815262532596</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.2956798459391326</v>
+        <v>0.2956798459391328</v>
       </c>
       <c r="BV5" t="n">
         <v>0.1646990402039556</v>
@@ -3809,7 +3819,7 @@
         <v>0.3314199407762891</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.3625718299170316</v>
+        <v>0.3625718299170317</v>
       </c>
       <c r="BY5" t="n">
         <v>0.1942059471608217</v>
@@ -3818,19 +3828,19 @@
         <v>0.3569160758765189</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.2175654139668449</v>
+        <v>0.217565413966845</v>
       </c>
       <c r="CB5" t="n">
         <v>0.2294256264236114</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.2490257766469354</v>
+        <v>0.2490257766469355</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.03693636182348328</v>
+        <v>0.03693636182348332</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.06697101682492271</v>
+        <v>0.06697101682492275</v>
       </c>
       <c r="CF5" t="n">
         <v>0.1020921179177291</v>
@@ -3851,16 +3861,16 @@
         <v>0.2908352850369444</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.2224993954816585</v>
+        <v>0.2224993954816584</v>
       </c>
       <c r="CM5" t="n">
         <v>0.3099404634007625</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.3312861569520005</v>
+        <v>0.3312861569520006</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.2470018451104411</v>
+        <v>0.247001845110441</v>
       </c>
       <c r="CP5" t="n">
         <v>0.3380777845178211</v>
@@ -3875,13 +3885,13 @@
         <v>0.2872506977087549</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.03616417875745195</v>
+        <v>0.03616417875745193</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0629430310248833</v>
+        <v>0.06294303102488329</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.09012288806160855</v>
+        <v>0.09012288806160856</v>
       </c>
       <c r="CW5" t="n">
         <v>0.1097789019684504</v>
@@ -3896,13 +3906,13 @@
         <v>0.2822444874095781</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.3102128229330282</v>
+        <v>0.3102128229330283</v>
       </c>
       <c r="DB5" t="n">
         <v>0.171141432279567</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.3401879510934792</v>
+        <v>0.3401879510934793</v>
       </c>
       <c r="DD5" t="n">
         <v>0.3561387219746954</v>
@@ -3911,19 +3921,19 @@
         <v>0.1956744694852246</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.3438255958268553</v>
+        <v>0.3438255958268554</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.2186484988161777</v>
+        <v>0.2186484988161778</v>
       </c>
       <c r="DH5" t="n">
         <v>0.2314680096888893</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.2603421665630949</v>
+        <v>0.2603421665630948</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.03915657394366524</v>
+        <v>0.03915657394366525</v>
       </c>
       <c r="DK5" t="n">
         <v>0.07046989757663724</v>
@@ -3935,13 +3945,13 @@
         <v>0.131610656386919</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.1553700616612763</v>
+        <v>0.1553700616612764</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.187809073318804</v>
+        <v>0.1878090733188039</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.2786955836652735</v>
+        <v>0.2786955836652736</v>
       </c>
       <c r="DQ5" t="n">
         <v>0.2826490048686331</v>
@@ -3953,28 +3963,28 @@
         <v>0.3114341265301121</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.3317849034715394</v>
+        <v>0.3317849034715395</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.2435813791490055</v>
+        <v>0.2435813791490054</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.3404089279700952</v>
+        <v>0.3404089279700953</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2599193742043693</v>
+        <v>0.2599193742043691</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.2746488573768897</v>
+        <v>0.2746488573768895</v>
       </c>
       <c r="DY5" t="n">
         <v>0.2814368021771715</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.04080140016737331</v>
+        <v>0.04080140016737333</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.07141436918172336</v>
+        <v>0.07141436918172335</v>
       </c>
       <c r="EB5" t="n">
         <v>0.1050120021827375</v>
@@ -3986,7 +3996,7 @@
         <v>0.1523652626125026</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.1876585464624627</v>
+        <v>0.1876585464624626</v>
       </c>
       <c r="EF5" t="n">
         <v>0.2803480988136748</v>
@@ -3998,22 +4008,22 @@
         <v>0.2103500800433075</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.3114788483492328</v>
+        <v>0.3114788483492327</v>
       </c>
       <c r="EJ5" t="n">
         <v>0.3295768650813336</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.2398114972968031</v>
+        <v>0.239811497296803</v>
       </c>
       <c r="EL5" t="n">
         <v>0.3476477609633097</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.2571584625934784</v>
+        <v>0.2571584625934785</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.2654513009222798</v>
+        <v>0.2654513009222799</v>
       </c>
       <c r="EO5" t="n">
         <v>0.2731598949668992</v>
@@ -4031,28 +4041,28 @@
         <v>0.1297897130741582</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.1508709564755121</v>
+        <v>0.150870956475512</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.1819711341058941</v>
+        <v>0.1819711341058939</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.2701461454926788</v>
+        <v>0.2701461454926787</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.2864193602606947</v>
+        <v>0.2864193602606948</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.2052975928837031</v>
+        <v>0.205297592883703</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.3091907169368881</v>
+        <v>0.3091907169368882</v>
       </c>
       <c r="EZ5" t="n">
         <v>0.3308807493005825</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.2294229967046719</v>
+        <v>0.2294229967046718</v>
       </c>
       <c r="FB5" t="n">
         <v>0.3470101466516467</v>
@@ -4064,13 +4074,13 @@
         <v>0.2619972617942528</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.2759946131927877</v>
+        <v>0.2759946131927878</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.04054755657717932</v>
+        <v>0.04054755657717934</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0697020153681091</v>
+        <v>0.06970201536810909</v>
       </c>
       <c r="FH5" t="n">
         <v>0.1039735248473535</v>
@@ -4106,7 +4116,7 @@
         <v>0.3455970541177442</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.2480419749548319</v>
+        <v>0.2480419749548318</v>
       </c>
       <c r="FT5" t="n">
         <v>0.2551565894893442</v>
@@ -4115,10 +4125,10 @@
         <v>0.2637111398102884</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.03992690894281054</v>
+        <v>0.03992690894281056</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.07085076994007869</v>
+        <v>0.07085076994007868</v>
       </c>
       <c r="FX5" t="n">
         <v>0.1004039286124287</v>
@@ -4127,7 +4137,7 @@
         <v>0.1246763461191915</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.1421074244657351</v>
+        <v>0.142107424465735</v>
       </c>
       <c r="GA5" t="n">
         <v>0.1721659745497896</v>
@@ -4139,7 +4149,7 @@
         <v>0.2842357753141925</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.1959010122791275</v>
+        <v>0.1959010122791274</v>
       </c>
       <c r="GE5" t="n">
         <v>0.3034887656364063</v>
@@ -4148,10 +4158,10 @@
         <v>0.330084198324181</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.2240253342834989</v>
+        <v>0.224025334283499</v>
       </c>
       <c r="GH5" t="n">
-        <v>0.348982997447415</v>
+        <v>0.3489829974474151</v>
       </c>
       <c r="GI5" t="n">
         <v>0.2395454725537378</v>
@@ -4169,37 +4179,37 @@
         <v>0.06989927390119549</v>
       </c>
       <c r="GN5" t="n">
-        <v>0.09867843352501816</v>
+        <v>0.09867843352501819</v>
       </c>
       <c r="GO5" t="n">
         <v>0.1229635875821244</v>
       </c>
       <c r="GP5" t="n">
-        <v>0.1384955929863931</v>
+        <v>0.138495592986393</v>
       </c>
       <c r="GQ5" t="n">
-        <v>0.1680383352230009</v>
+        <v>0.1680383352230008</v>
       </c>
       <c r="GR5" t="n">
         <v>0.2673571977068037</v>
       </c>
       <c r="GS5" t="n">
-        <v>0.2822322822965824</v>
+        <v>0.2822322822965825</v>
       </c>
       <c r="GT5" t="n">
-        <v>0.1884229640625081</v>
+        <v>0.188422964062508</v>
       </c>
       <c r="GU5" t="n">
         <v>0.3024032181439458</v>
       </c>
       <c r="GV5" t="n">
-        <v>0.3244386612925418</v>
+        <v>0.3244386612925419</v>
       </c>
       <c r="GW5" t="n">
-        <v>0.2180932249294947</v>
+        <v>0.2180932249294946</v>
       </c>
       <c r="GX5" t="n">
-        <v>0.342927343072703</v>
+        <v>0.3429273430727031</v>
       </c>
       <c r="GY5" t="n">
         <v>0.2323902985386768</v>
@@ -4208,16 +4218,16 @@
         <v>0.2475847271930774</v>
       </c>
       <c r="HA5" t="n">
-        <v>0.2549534824452862</v>
+        <v>0.2549534824452861</v>
       </c>
       <c r="HB5" t="n">
-        <v>0.03975773950280988</v>
+        <v>0.03975773950280989</v>
       </c>
       <c r="HC5" t="n">
-        <v>0.06971716694878445</v>
+        <v>0.06971716694878442</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.09954489641384112</v>
+        <v>0.09954489641384111</v>
       </c>
       <c r="HE5" t="n">
         <v>0.1220382388399908</v>
@@ -4235,19 +4245,19 @@
         <v>0.2837804728252624</v>
       </c>
       <c r="HJ5" t="n">
-        <v>0.1865168916260494</v>
+        <v>0.1865168916260493</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.3036201964766207</v>
+        <v>0.3036201964766208</v>
       </c>
       <c r="HL5" t="n">
-        <v>0.3255170824186279</v>
+        <v>0.325517082418628</v>
       </c>
       <c r="HM5" t="n">
         <v>0.2152698824504508</v>
       </c>
       <c r="HN5" t="n">
-        <v>0.3456617076516389</v>
+        <v>0.345661707651639</v>
       </c>
       <c r="HO5" t="n">
         <v>0.2291476529471297</v>
@@ -4260,19 +4270,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30/12/2051</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>55517</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03907627936509393</v>
+        <v>0.03907627936509392</v>
       </c>
       <c r="C6" t="n">
         <v>0.06924012927333921</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09588686533330026</v>
+        <v>0.09588686533330025</v>
       </c>
       <c r="E6" t="n">
         <v>0.1170667561962742</v>
@@ -4281,7 +4289,7 @@
         <v>0.1375399681247296</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1596236006029897</v>
+        <v>0.1596236006029896</v>
       </c>
       <c r="H6" t="n">
         <v>0.2612115964568033</v>
@@ -4290,7 +4298,7 @@
         <v>0.2836073597849977</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1859159761736282</v>
+        <v>0.1859159761736281</v>
       </c>
       <c r="K6" t="n">
         <v>0.3059914820214877</v>
@@ -4299,7 +4307,7 @@
         <v>0.3247429169051272</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2081208277865775</v>
+        <v>0.2081208277865776</v>
       </c>
       <c r="N6" t="n">
         <v>0.3426315126670534</v>
@@ -4314,10 +4322,10 @@
         <v>0.2556835782226553</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0377645907128102</v>
+        <v>0.03776459071281021</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06549446011462191</v>
+        <v>0.06549446011462193</v>
       </c>
       <c r="T6" t="n">
         <v>0.09005279722619515</v>
@@ -4344,10 +4352,10 @@
         <v>0.3107373106731301</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3365308220430618</v>
+        <v>0.3365308220430619</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1997743222596358</v>
+        <v>0.1997743222596357</v>
       </c>
       <c r="AD6" t="n">
         <v>0.3647462330553162</v>
@@ -4359,13 +4367,13 @@
         <v>0.227153241378655</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2512456839193779</v>
+        <v>0.251245683919378</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.02828830885883867</v>
+        <v>0.02828830885883872</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.05512414005993915</v>
+        <v>0.05512414005993917</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.08931716523964343</v>
@@ -4374,7 +4382,7 @@
         <v>0.1207918794298067</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1537495277504487</v>
+        <v>0.1537495277504488</v>
       </c>
       <c r="AM6" t="n">
         <v>0.1952192937731609</v>
@@ -4395,34 +4403,34 @@
         <v>0.334946126166891</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.2590130212093042</v>
+        <v>0.2590130212093041</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.3428464637491877</v>
+        <v>0.3428464637491879</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2745801779774657</v>
+        <v>0.2745801779774656</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.2877369554544941</v>
+        <v>0.287736955454494</v>
       </c>
       <c r="AW6" t="n">
         <v>0.2929332818357506</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.03595877587884389</v>
+        <v>0.0359587758788439</v>
       </c>
       <c r="AY6" t="n">
         <v>0.06192907788045338</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.08714228841107063</v>
+        <v>0.08714228841107065</v>
       </c>
       <c r="BA6" t="n">
         <v>0.1081648403478039</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1250293868439628</v>
+        <v>0.1250293868439629</v>
       </c>
       <c r="BC6" t="n">
         <v>0.1450450441662129</v>
@@ -4434,13 +4442,13 @@
         <v>0.2905604569633484</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1649218081108376</v>
+        <v>0.1649218081108377</v>
       </c>
       <c r="BG6" t="n">
         <v>0.3153959826617648</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.3496350452472754</v>
+        <v>0.3496350452472756</v>
       </c>
       <c r="BI6" t="n">
         <v>0.1958501127908127</v>
@@ -4452,16 +4460,16 @@
         <v>0.2150815031326986</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.2294585059432305</v>
+        <v>0.2294585059432306</v>
       </c>
       <c r="BM6" t="n">
         <v>0.2498714810116066</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.03577245519198533</v>
+        <v>0.03577245519198532</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.06178092623990831</v>
+        <v>0.06178092623990833</v>
       </c>
       <c r="BP6" t="n">
         <v>0.08945728991701307</v>
@@ -4473,46 +4481,46 @@
         <v>0.1240100843477745</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1448018266470164</v>
+        <v>0.1448018266470163</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.271885055344441</v>
+        <v>0.2718850553444411</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.2950476061635307</v>
+        <v>0.2950476061635308</v>
       </c>
       <c r="BV6" t="n">
         <v>0.1640731321461996</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.330597673621547</v>
+        <v>0.3305976736215469</v>
       </c>
       <c r="BX6" t="n">
         <v>0.3618116029569019</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1934556150255552</v>
+        <v>0.1934556150255551</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.356532347202687</v>
+        <v>0.3565323472026871</v>
       </c>
       <c r="CA6" t="n">
         <v>0.216822375008661</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.2288165312831797</v>
+        <v>0.2288165312831798</v>
       </c>
       <c r="CC6" t="n">
         <v>0.2484923171790474</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.03766929443391367</v>
+        <v>0.03766929443391368</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0681707530616566</v>
+        <v>0.06817075306165665</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.1036976922789362</v>
+        <v>0.1036976922789363</v>
       </c>
       <c r="CG6" t="n">
         <v>0.1324989085655861</v>
@@ -4521,16 +4529,16 @@
         <v>0.1579252057284205</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1938315773724177</v>
+        <v>0.1938315773724176</v>
       </c>
       <c r="CJ6" t="n">
         <v>0.2894749110829795</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.2905523355262879</v>
+        <v>0.290552335526288</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.2227992563201006</v>
+        <v>0.2227992563201004</v>
       </c>
       <c r="CM6" t="n">
         <v>0.3091408113346947</v>
@@ -4539,28 +4547,28 @@
         <v>0.3304587866349053</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.2465588383132178</v>
+        <v>0.2465588383132177</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.3374855048519563</v>
+        <v>0.3374855048519564</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.267913688260299</v>
+        <v>0.2679136882602989</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.276432954616289</v>
+        <v>0.2764329546162889</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.2863390243631881</v>
+        <v>0.286339024363188</v>
       </c>
       <c r="CT6" t="n">
         <v>0.03609796735068383</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.06276170268487573</v>
+        <v>0.06276170268487571</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.08974746487532255</v>
+        <v>0.08974746487532254</v>
       </c>
       <c r="CW6" t="n">
         <v>0.1092870834128031</v>
@@ -4569,13 +4577,13 @@
         <v>0.1232237276365735</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.1474889063235064</v>
+        <v>0.1474889063235063</v>
       </c>
       <c r="CZ6" t="n">
         <v>0.2818195396659036</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.3096305934454248</v>
+        <v>0.3096305934454249</v>
       </c>
       <c r="DB6" t="n">
         <v>0.1704153085996223</v>
@@ -4599,13 +4607,13 @@
         <v>0.2307828164741985</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.2598712346602297</v>
+        <v>0.2598712346602298</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.03986413070027652</v>
+        <v>0.03986413070027655</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.07158726194751</v>
+        <v>0.07158726194751003</v>
       </c>
       <c r="DL6" t="n">
         <v>0.1045723675357568</v>
@@ -4614,10 +4622,10 @@
         <v>0.1329419805540298</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.1564307367353461</v>
+        <v>0.156430736735346</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.1884838396578465</v>
+        <v>0.1884838396578464</v>
       </c>
       <c r="DP6" t="n">
         <v>0.2783087441270848</v>
@@ -4626,46 +4634,46 @@
         <v>0.2823394023764134</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.2165867243857063</v>
+        <v>0.2165867243857062</v>
       </c>
       <c r="DS6" t="n">
         <v>0.3105891327476473</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.3308220570987423</v>
+        <v>0.3308220570987424</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.2431099920685271</v>
+        <v>0.243109992068527</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.3397252473727592</v>
+        <v>0.3397252473727594</v>
       </c>
       <c r="DW6" t="n">
         <v>0.2590934213691727</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.2737416261707376</v>
+        <v>0.2737416261707374</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.2806671700147976</v>
+        <v>0.2806671700147975</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.04143142401193358</v>
+        <v>0.04143142401193359</v>
       </c>
       <c r="EA6" t="n">
         <v>0.07231029347841371</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.1059981216899757</v>
+        <v>0.1059981216899758</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.1331133035168906</v>
+        <v>0.1331133035168905</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.1529385402663785</v>
+        <v>0.1529385402663784</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.1878266639254792</v>
+        <v>0.1878266639254791</v>
       </c>
       <c r="EF6" t="n">
         <v>0.2799894362549741</v>
@@ -4674,22 +4682,22 @@
         <v>0.2801189428509857</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.2101479272984058</v>
+        <v>0.2101479272984057</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.3106134824822151</v>
+        <v>0.3106134824822152</v>
       </c>
       <c r="EJ6" t="n">
         <v>0.3286599446676203</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.2392839877757277</v>
+        <v>0.2392839877757276</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.3468560682166739</v>
+        <v>0.346856068216674</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.2562935485425979</v>
+        <v>0.2562935485425978</v>
       </c>
       <c r="EN6" t="n">
         <v>0.2644789667646091</v>
@@ -4710,7 +4718,7 @@
         <v>0.130490716471629</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.1513009878514762</v>
+        <v>0.1513009878514761</v>
       </c>
       <c r="EU6" t="n">
         <v>0.1820677781448962</v>
@@ -4719,10 +4727,10 @@
         <v>0.26981313557755</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.2860945674439269</v>
+        <v>0.286094567443927</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.2049872313163877</v>
+        <v>0.2049872313163876</v>
       </c>
       <c r="EY6" t="n">
         <v>0.3082770806355892</v>
@@ -4734,31 +4742,31 @@
         <v>0.2286882554391723</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.3461892274859688</v>
+        <v>0.3461892274859689</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2473349225441673</v>
+        <v>0.2473349225441672</v>
       </c>
       <c r="FD6" t="n">
         <v>0.2611790696092248</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.2752715699644672</v>
+        <v>0.2752715699644673</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.04099545666577253</v>
+        <v>0.04099545666577251</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.07027600584369094</v>
+        <v>0.07027600584369093</v>
       </c>
       <c r="FH6" t="n">
         <v>0.1045499896868394</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.1249582115119414</v>
+        <v>0.1249582115119413</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.143489052276097</v>
+        <v>0.1434890522760971</v>
       </c>
       <c r="FK6" t="n">
         <v>0.176474259269453</v>
@@ -4779,10 +4787,10 @@
         <v>0.3238209705117367</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.2240257366928806</v>
+        <v>0.2240257366928804</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.3447563341781761</v>
+        <v>0.3447563341781762</v>
       </c>
       <c r="FS6" t="n">
         <v>0.2470247308277449</v>
@@ -4797,7 +4805,7 @@
         <v>0.04025682945715162</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.07129266462184124</v>
+        <v>0.07129266462184126</v>
       </c>
       <c r="FX6" t="n">
         <v>0.1007649894657155</v>
@@ -4806,7 +4814,7 @@
         <v>0.1249336688724982</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.1421454489746177</v>
+        <v>0.1421454489746176</v>
       </c>
       <c r="GA6" t="n">
         <v>0.1719163675089697</v>
@@ -4815,16 +4823,16 @@
         <v>0.2705536939827397</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.2837906674508573</v>
+        <v>0.2837906674508574</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.1954336124704317</v>
+        <v>0.1954336124704316</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.302444073795945</v>
+        <v>0.3024440737959451</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3291230088924254</v>
+        <v>0.3291230088924255</v>
       </c>
       <c r="GG6" t="n">
         <v>0.2232253834104775</v>
@@ -4833,16 +4841,16 @@
         <v>0.3480981095385174</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.2387162415557213</v>
+        <v>0.2387162415557212</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.2500104068829563</v>
+        <v>0.2500104068829562</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.2628935486114887</v>
+        <v>0.2628935486114888</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.03987749344845162</v>
+        <v>0.03987749344845163</v>
       </c>
       <c r="GM6" t="n">
         <v>0.07018886862309516</v>
@@ -4857,28 +4865,28 @@
         <v>0.1384204553783705</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.1676996884999848</v>
+        <v>0.1676996884999847</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.2670071815662503</v>
+        <v>0.2670071815662504</v>
       </c>
       <c r="GS6" t="n">
         <v>0.2817542318643814</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.1878635079951557</v>
+        <v>0.1878635079951556</v>
       </c>
       <c r="GU6" t="n">
         <v>0.3011979018365309</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.3235244624843525</v>
+        <v>0.3235244624843526</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.2172447257778118</v>
+        <v>0.2172447257778117</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.3420254820850748</v>
+        <v>0.3420254820850749</v>
       </c>
       <c r="GY6" t="n">
         <v>0.2315998399372854</v>
@@ -4887,22 +4895,22 @@
         <v>0.2469390745427102</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.2544815527056492</v>
+        <v>0.2544815527056491</v>
       </c>
       <c r="HB6" t="n">
         <v>0.03997605870571513</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.06990939069674762</v>
+        <v>0.06990939069674761</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.09963792045118817</v>
+        <v>0.09963792045118815</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.122011865266862</v>
+        <v>0.1220118652668619</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.1368309824183994</v>
+        <v>0.1368309824183993</v>
       </c>
       <c r="HG6" t="n">
         <v>0.1647468883039127</v>
@@ -4911,22 +4919,22 @@
         <v>0.2625133777060218</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.2832296126390701</v>
+        <v>0.2832296126390702</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.1858798970860796</v>
+        <v>0.1858798970860795</v>
       </c>
       <c r="HK6" t="n">
         <v>0.3026316205328978</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.3245991063806413</v>
+        <v>0.3245991063806414</v>
       </c>
       <c r="HM6" t="n">
         <v>0.2146150456592249</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.3446862080904822</v>
+        <v>0.3446862080904823</v>
       </c>
       <c r="HO6" t="n">
         <v>0.2284639801684676</v>
@@ -4939,19 +4947,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>01/01/2052</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>55519</v>
       </c>
       <c r="B7" t="n">
         <v>0.03982320259432751</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07038003904967312</v>
+        <v>0.07038003904967315</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09726581598692159</v>
+        <v>0.09726581598692158</v>
       </c>
       <c r="E7" t="n">
         <v>0.118576504862553</v>
@@ -4960,7 +4966,7 @@
         <v>0.139220412545129</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1614164470005714</v>
+        <v>0.1614164470005713</v>
       </c>
       <c r="H7" t="n">
         <v>0.2620292820257518</v>
@@ -4972,16 +4978,16 @@
         <v>0.1878772905179535</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3072408147665185</v>
+        <v>0.3072408147665184</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3260993226427664</v>
+        <v>0.3260993226427665</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2098551517665897</v>
+        <v>0.2098551517665896</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3448132985269243</v>
+        <v>0.3448132985269244</v>
       </c>
       <c r="O7" t="n">
         <v>0.2254933170312617</v>
@@ -4990,16 +4996,16 @@
         <v>0.2431467563622023</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2567360367038822</v>
+        <v>0.2567360367038823</v>
       </c>
       <c r="R7" t="n">
         <v>0.03844793853977917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06652101925351893</v>
+        <v>0.06652101925351894</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09119885324961081</v>
+        <v>0.0911988532496108</v>
       </c>
       <c r="U7" t="n">
         <v>0.1121749159312804</v>
@@ -5011,25 +5017,25 @@
         <v>0.1554732808895687</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2634087133220917</v>
+        <v>0.2634087133220918</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2820550690721759</v>
+        <v>0.282055069072176</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1708530050487332</v>
+        <v>0.1708530050487333</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3118692387256498</v>
+        <v>0.3118692387256499</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3378703158163716</v>
+        <v>0.3378703158163717</v>
       </c>
       <c r="AC7" t="n">
         <v>0.2011233773799899</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3668205370171866</v>
+        <v>0.3668205370171867</v>
       </c>
       <c r="AE7" t="n">
         <v>0.2194010248972764</v>
@@ -5041,13 +5047,13 @@
         <v>0.2521549259369555</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.02901808926842347</v>
+        <v>0.02901808926842352</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.05618777379495762</v>
+        <v>0.05618777379495768</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09079520278946647</v>
+        <v>0.09079520278946658</v>
       </c>
       <c r="AK7" t="n">
         <v>0.1226214032234759</v>
@@ -5056,7 +5062,7 @@
         <v>0.1561340291346155</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.198557434371995</v>
+        <v>0.1985574343719951</v>
       </c>
       <c r="AN7" t="n">
         <v>0.2906657478997406</v>
@@ -5068,22 +5074,22 @@
         <v>0.2261726841643595</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.3097397648261492</v>
+        <v>0.3097397648261493</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.3363040802376636</v>
+        <v>0.3363040802376637</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.2624592653804151</v>
+        <v>0.2624592653804152</v>
       </c>
       <c r="AT7" t="n">
         <v>0.3445982576697837</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2782126465336438</v>
+        <v>0.2782126465336437</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2909844985536496</v>
+        <v>0.2909844985536494</v>
       </c>
       <c r="AW7" t="n">
         <v>0.2954450166816893</v>
@@ -5092,13 +5098,13 @@
         <v>0.03651573107878839</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.06277142814467378</v>
+        <v>0.06277142814467379</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.08816696078250082</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1093044810230627</v>
+        <v>0.1093044810230628</v>
       </c>
       <c r="BB7" t="n">
         <v>0.1262008056390271</v>
@@ -5110,28 +5116,28 @@
         <v>0.2636902821949269</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.291291119696445</v>
+        <v>0.2912911196964451</v>
       </c>
       <c r="BF7" t="n">
         <v>0.1661611157296022</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.3164964309075509</v>
+        <v>0.316496430907551</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.3509717427615225</v>
+        <v>0.3509717427615226</v>
       </c>
       <c r="BI7" t="n">
         <v>0.1971477437017806</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.3799290898793696</v>
+        <v>0.3799290898793697</v>
       </c>
       <c r="BK7" t="n">
         <v>0.2160643140657844</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.2304905415946374</v>
+        <v>0.2304905415946375</v>
       </c>
       <c r="BM7" t="n">
         <v>0.2506294584147116</v>
@@ -5140,13 +5146,13 @@
         <v>0.03631339925036645</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06262807483768119</v>
+        <v>0.06262807483768122</v>
       </c>
       <c r="BP7" t="n">
         <v>0.09050412986982688</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.107554488154579</v>
+        <v>0.1075544881545789</v>
       </c>
       <c r="BR7" t="n">
         <v>0.1251621134516324</v>
@@ -5155,16 +5161,16 @@
         <v>0.1460410165826349</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.2724869110347354</v>
+        <v>0.2724869110347355</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.2958517518434791</v>
+        <v>0.2958517518434792</v>
       </c>
       <c r="BV7" t="n">
         <v>0.165230997320529</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.3316998607721193</v>
+        <v>0.3316998607721195</v>
       </c>
       <c r="BX7" t="n">
         <v>0.3633092710850483</v>
@@ -5173,22 +5179,22 @@
         <v>0.1946078926224124</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.3580259863441597</v>
+        <v>0.3580259863441598</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.217839103999637</v>
+        <v>0.2178391039996371</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.2296485285564044</v>
+        <v>0.2296485285564045</v>
       </c>
       <c r="CC7" t="n">
         <v>0.2491511623100814</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.03853885568937518</v>
+        <v>0.03853885568937521</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.06953393234805305</v>
+        <v>0.06953393234805309</v>
       </c>
       <c r="CF7" t="n">
         <v>0.1055463521442539</v>
@@ -5200,7 +5206,7 @@
         <v>0.1605673322983268</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.1969665706794443</v>
+        <v>0.1969665706794441</v>
       </c>
       <c r="CJ7" t="n">
         <v>0.2906149522647805</v>
@@ -5209,31 +5215,31 @@
         <v>0.2914921824883021</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.2263725768113262</v>
+        <v>0.226372576811326</v>
       </c>
       <c r="CM7" t="n">
         <v>0.3104764575504179</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.3316672782692784</v>
+        <v>0.3316672782692785</v>
       </c>
       <c r="CO7" t="n">
         <v>0.2502041078251474</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.339151079975993</v>
+        <v>0.3391510799759931</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.2711606545620659</v>
+        <v>0.2711606545620658</v>
       </c>
       <c r="CR7" t="n">
         <v>0.2794449760644955</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.2884152392553377</v>
+        <v>0.2884152392553376</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.03660734970059122</v>
+        <v>0.03660734970059124</v>
       </c>
       <c r="CU7" t="n">
         <v>0.06354293030258677</v>
@@ -5248,10 +5254,10 @@
         <v>0.1243134602008473</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1486430301723991</v>
+        <v>0.148643030172399</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.2824462716861906</v>
+        <v>0.2824462716861907</v>
       </c>
       <c r="DA7" t="n">
         <v>0.3105581345700199</v>
@@ -5263,13 +5269,13 @@
         <v>0.3406428127453299</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.3566048068487261</v>
+        <v>0.3566048068487262</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1959943128678013</v>
+        <v>0.1959943128678014</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.3445836879395961</v>
+        <v>0.3445836879395962</v>
       </c>
       <c r="DG7" t="n">
         <v>0.2188835376691728</v>
@@ -5278,16 +5284,16 @@
         <v>0.2316682174432961</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.2607474698513002</v>
+        <v>0.2607474698513003</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.04075143039335529</v>
+        <v>0.0407514303933553</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.07307882609155758</v>
+        <v>0.07307882609155759</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.1065545379433277</v>
+        <v>0.1065545379433278</v>
       </c>
       <c r="DM7" t="n">
         <v>0.1353370368418355</v>
@@ -5296,13 +5302,13 @@
         <v>0.1589157903500596</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.1916573380070079</v>
+        <v>0.1916573380070078</v>
       </c>
       <c r="DP7" t="n">
         <v>0.2793355960325148</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.2832346675552901</v>
+        <v>0.2832346675552902</v>
       </c>
       <c r="DR7" t="n">
         <v>0.2198957712807343</v>
@@ -5317,7 +5323,7 @@
         <v>0.2462557145968521</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.34147627551733</v>
+        <v>0.3414762755173302</v>
       </c>
       <c r="DW7" t="n">
         <v>0.2621951154214837</v>
@@ -5326,13 +5332,13 @@
         <v>0.2766004339212809</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.2824993426606102</v>
+        <v>0.2824993426606101</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.04232812587902698</v>
+        <v>0.04232812587902701</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.07372984127106455</v>
+        <v>0.07372984127106456</v>
       </c>
       <c r="EB7" t="n">
         <v>0.1078189808886995</v>
@@ -5344,16 +5350,16 @@
         <v>0.1553252961935733</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.1908187384690517</v>
+        <v>0.1908187384690516</v>
       </c>
       <c r="EF7" t="n">
         <v>0.2809358903930312</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.2809541108392167</v>
+        <v>0.2809541108392168</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.2130947371194219</v>
+        <v>0.2130947371194218</v>
       </c>
       <c r="EI7" t="n">
         <v>0.3120666956737511</v>
@@ -5365,31 +5371,31 @@
         <v>0.2422544646718966</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.3486696146685921</v>
+        <v>0.3486696146685923</v>
       </c>
       <c r="EM7" t="n">
         <v>0.2591994010462019</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.2669649538625523</v>
+        <v>0.2669649538625522</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.2740145420875377</v>
+        <v>0.2740145420875378</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.04281911131662241</v>
+        <v>0.04281911131662242</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.07498088517687573</v>
+        <v>0.07498088517687575</v>
       </c>
       <c r="ER7" t="n">
         <v>0.1075623344725853</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1325968664429152</v>
+        <v>0.1325968664429153</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.1535597487034369</v>
+        <v>0.1535597487034368</v>
       </c>
       <c r="EU7" t="n">
         <v>0.1845828209393045</v>
@@ -5398,28 +5404,28 @@
         <v>0.2706985801808383</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.2870394170517829</v>
+        <v>0.287039417051783</v>
       </c>
       <c r="EX7" t="n">
         <v>0.2077968930603717</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.3096541393491841</v>
+        <v>0.3096541393491842</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.3312293445749611</v>
+        <v>0.3312293445749612</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.2314583341851694</v>
+        <v>0.2314583341851695</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.348065816492172</v>
+        <v>0.3480658164921722</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2499741746403547</v>
+        <v>0.2499741746403548</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.2633467565027952</v>
+        <v>0.2633467565027951</v>
       </c>
       <c r="FE7" t="n">
         <v>0.276803739159257</v>
@@ -5443,10 +5449,10 @@
         <v>0.1788578253047096</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.2717315287637457</v>
+        <v>0.2717315287637458</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.284191397835989</v>
+        <v>0.2841913978359891</v>
       </c>
       <c r="FN7" t="n">
         <v>0.1984558284431414</v>
@@ -5458,10 +5464,10 @@
         <v>0.3250869446891873</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.2266374743492804</v>
+        <v>0.2266374743492803</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.3466680002537408</v>
+        <v>0.346668000253741</v>
       </c>
       <c r="FS7" t="n">
         <v>0.249389750927944</v>
@@ -5473,7 +5479,7 @@
         <v>0.2644028407903654</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.04106571405728594</v>
+        <v>0.04106571405728595</v>
       </c>
       <c r="FW7" t="n">
         <v>0.07256010571029343</v>
@@ -5494,13 +5500,13 @@
         <v>0.2713923689285448</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.2847336970506939</v>
+        <v>0.284733697050694</v>
       </c>
       <c r="GD7" t="n">
         <v>0.1977885006119006</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.3037360637896657</v>
+        <v>0.3037360637896658</v>
       </c>
       <c r="GF7" t="n">
         <v>0.330417966932326</v>
@@ -5512,7 +5518,7 @@
         <v>0.3500831963356024</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.2407544300380964</v>
+        <v>0.2407544300380963</v>
       </c>
       <c r="GJ7" t="n">
         <v>0.2518202518650683</v>
@@ -5524,19 +5530,19 @@
         <v>0.04067851059771355</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.07135115083329523</v>
+        <v>0.07135115083329524</v>
       </c>
       <c r="GN7" t="n">
         <v>0.1003156011683878</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.1247132294698615</v>
+        <v>0.1247132294698616</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.1401827285577475</v>
+        <v>0.1401827285577476</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.1698013254467307</v>
+        <v>0.1698013254467306</v>
       </c>
       <c r="GR7" t="n">
         <v>0.2678373920418387</v>
@@ -5548,16 +5554,16 @@
         <v>0.1900618536044985</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3023235794474954</v>
+        <v>0.3023235794474955</v>
       </c>
       <c r="GV7" t="n">
-        <v>0.3248081181986442</v>
+        <v>0.3248081181986444</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.2194056507171607</v>
+        <v>0.2194056507171605</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3440413802820367</v>
+        <v>0.3440413802820368</v>
       </c>
       <c r="GY7" t="n">
         <v>0.2334918233891037</v>
@@ -5569,10 +5575,10 @@
         <v>0.2557526675142033</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.04075938899504738</v>
+        <v>0.04075938899504739</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.07110550880799472</v>
+        <v>0.07110550880799471</v>
       </c>
       <c r="HD7" t="n">
         <v>0.1011438555650411</v>
@@ -5599,19 +5605,19 @@
         <v>0.3038846858534479</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.3259237125289114</v>
+        <v>0.3259237125289116</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.2165326737036159</v>
+        <v>0.216532673703616</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.346783698690023</v>
+        <v>0.3467836986900231</v>
       </c>
       <c r="HO7" t="n">
         <v>0.230136844268741</v>
       </c>
       <c r="HP7" t="n">
-        <v>0.2461372316292076</v>
+        <v>0.2461372316292077</v>
       </c>
       <c r="HQ7" t="n">
         <v>0.2587960791610737</v>
